--- a/Hardware/EET_BMS_Layout/bom/BOM_2026.xlsx
+++ b/Hardware/EET_BMS_Layout/bom/BOM_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavel\Nextcloud\Arbeit\BMS Paper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavel\Nextcloud\Arbeit\Projekte\STM32_Projekte\Open_BMS\Open_BMS\Hardware\EET_BMS_Layout\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07D3861-0901-4DE5-94D6-E9AB82AA30D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41147EB-67F9-4154-99C1-AB696993EE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{85166753-1B09-4F80-A3D3-B99E6B9AA4E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{85166753-1B09-4F80-A3D3-B99E6B9AA4E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="172">
   <si>
     <t>References</t>
   </si>
@@ -446,127 +446,115 @@
     <t>Ordernumber</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/details/adum1200arz/integ-schalt-sonstige-schnittstellen/analog-devices/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/thvd1500d/integ-schalt-rs232-rs422-rs485/texas-instruments/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/cl21b102kbannnc/kondensatoren-mlcc-smd/samsung/</t>
-  </si>
-  <si>
     <t>Euro</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/details/cc0805krx7r9103/kondensatoren-mlcc-smd/yageo/cc0805krx7r9bb103/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/pf1j100mnn0511u/elektrolytische-kondensatoren-tht/elite/</t>
-  </si>
-  <si>
-    <t>50Stk</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/cl21a475kpfnnng/kondensatoren-mlcc-smd/samsung/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/cl21b225kafnnne/kondensatoren-mlcc-smd/samsung/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/cc0805kkx7r9bb334/kondensatoren-mlcc-smd/yageo/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/cc0805kkx5r8bb105/kondensatoren-mlcc-smd/yageo/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/c0805c270j5gac/kondensatoren-mlcc-smd/kemet/c0805c270j5gactu/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/crg0805f100r/smd-widerstande/te-connectivity/1623096-1/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/crcw08051k00fktabc/smd-widerstande/vishay/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/crcw080510r0fktabc/smd-widerstande/vishay/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/hp06-47r1%25/smd-widerstande/royalohm/hp06w2f470jt5e/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/smd0805-470r-1%25/smd-widerstande/royalohm/0805s8f4700t5e/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/smd0805-33k-1%25/smd-widerstande/royalohm/0805s8f3302t5e/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/crcw08050000z0tabc/smd-widerstande/vishay/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/mar251202fr005s/smd-widerstande/wayon/</t>
-  </si>
-  <si>
-    <t>MAR251202FR005S</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/erj6geyj5r1v/smd-widerstande/panasonic/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/erj6enf1002v/smd-widerstande/panasonic/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/fyls-0805pgc/led-dioden-smd-bunt/foryard/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/mmsz4683-tp/zener-dioden-smd/micro-commercial-components/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/lf33cv/ldo-festspannungsregler/stmicroelectronics/</t>
-  </si>
-  <si>
-    <t>https://www.mouser.de/ProductDetail/STMicroelectronics/TSC2012IDT?qs=%252B6g0mu59x7KSqOHhuXDI4w%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/16.00m-smdhc49s/quarzresonatoren-smd/yic/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/sud19p06-60-ge3/p-kanal-transistoren-smd/vishay/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/rfm-0505s/dc-dc-wandler/recom/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/bss138a-tp/n-kanal-transistoren-smd/micro-commercial-components/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/b2b-xh-a/signalsteckverbinder-raster-2-50mm/jst/b2b-xh-a-lf-sn/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/b7b-xh-a/signalsteckverbinder-raster-2-50mm/jst/b7b-xh-a-lf-sn/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/zl262-4sg/stiftleisten-und-buchsen/connfly/ds1023-1-4s21/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/b4b-xh-a/signalsteckverbinder-raster-2-50mm/jst/b4b-xh-a-lf-sn/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/zl202-40g/stiftleisten-und-buchsen/connfly/ds1021-2-20sf11-b/</t>
-  </si>
-  <si>
-    <t>https://www.tme.eu/de/details/zl262-40dg/stiftleisten-und-buchsen/connfly/ds1023-2-20s21/</t>
-  </si>
-  <si>
     <t>https://estore.st.com/en/stm32h755zit6-cpn.html</t>
   </si>
   <si>
-    <t>Dollar</t>
-  </si>
-  <si>
     <t>https://www.infineon.com/part/tle9012dqu</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/details/0805b104k500ct/kondensatoren-mlcc-smd/walsin/</t>
+    <t>https://www.tme.eu/en/details/0805b104k500ct/mlcc-smd-capacitors/walsin/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/cc0805krx7r9bb103/mlcc-smd-capacitors/yageo/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/pf1j100mnn0511u/tht-electrolytic-capacitors/elite/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/cl21a475kpfnnng/mlcc-smd-capacitors/samsung/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/crg0805f100r/smd-resistors/te-connectivity/1623096-1/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/smd0805-33k-1%25/smd-resistors/royalohm/0805s8f3302t5e/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/smd0805-470r-1%25/smd-resistors/royalohm/0805s8f4700t5e/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/hp06-47r1%25/smd-resistors/royalohm/hp06w2f470jt5e/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/crcw080510r0fktabc/smd-resistors/vishay/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/crcw08051k00fktabc/smd-resistors/vishay/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/c0805c270j5gac/mlcc-smd-capacitors/kemet/c0805c270j5gactu/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/cc0805kkx5r8bb105/mlcc-smd-capacitors/yageo/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/cc0805kkx7r9bb334/mlcc-smd-capacitors/yageo/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/cl21b225kafnnne/mlcc-smd-capacitors/samsung/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/cl21b102kbannnc/mlcc-smd-capacitors/samsung/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/mar251202fr005s/smd-resistors/wayon/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/erj6geyj5r1v/smd-resistors/panasonic/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/erj6enf1002v/smd-resistors/panasonic/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/fyls-0805pgc/smd-colour-leds/foryard/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/mmsz4683-tp/smd-zener-diodes/micro-commercial-components/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/lf33cv/ldo-fixed-voltage-regulators/stmicroelectronics/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/adum1200arz/interfaces-others-integrated-circuits/analog-devices/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/thvd1500d/rs232-rs422-rs485-integr-circ/texas-instruments/</t>
+  </si>
+  <si>
+    <t>https://eu.mouser.com/en/ProductDetail/STMicroelectronics/TSC2012IDT?qs=%252B6g0mu59x7KSqOHhuXDI4w%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/16.00m-smdhc49s/quarzresonatoren-smd/yic/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/sud19p06-60-ge3/smd-p-channel-transistors/vishay/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/rfm-0505s/dc-dc-converters/recom/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/bss138a-tp/smd-n-channel-transistors/micro-commercial-components/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/b2b-xh-a/raster-signal-connectors-2-50mm/jst/b2b-xh-a-lf-sn/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/b7b-xh-a/raster-signal-connectors-2-50mm/jst/b7b-xh-a-lf-sn/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/zl262-4sg/pin-headers/connfly/ds1023-1-4s21/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/b4b-xh-a/raster-signal-connectors-2-50mm/jst/b4b-xh-a-lf-sn/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/zl202-40g/pin-headers/connfly/ds1021-2-20sf11-b/</t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/en/details/zl262-40dg/pin-headers/connfly/ds1023-2-20s21/</t>
   </si>
 </sst>
 </file>
@@ -784,6 +772,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -794,12 +788,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1150,7 +1138,7 @@
     <col min="9" max="9" width="13.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="1.5703125" style="1" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" style="1"/>
-    <col min="12" max="12" width="10.85546875" style="24"/>
+    <col min="12" max="12" width="10.85546875" style="20"/>
     <col min="13" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
@@ -1184,7 +1172,7 @@
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
@@ -1218,10 +1206,10 @@
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="1">
-        <v>1.07</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>175</v>
+        <v>2.12</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1255,10 +1243,10 @@
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="1">
-        <v>0.31</v>
-      </c>
-      <c r="L3" s="24" t="s">
-        <v>137</v>
+        <v>0.45</v>
+      </c>
+      <c r="L3" s="21" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1293,9 +1281,9 @@
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="L4" s="24" t="s">
+        <v>0.63</v>
+      </c>
+      <c r="L4" s="21" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1330,13 +1318,10 @@
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="1">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="L5" s="24" t="s">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L5" s="21" t="s">
         <v>140</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1370,10 +1355,10 @@
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="1">
-        <v>0.31</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>142</v>
+        <v>0.37</v>
+      </c>
+      <c r="L6" s="21" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1407,10 +1392,10 @@
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="1">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>143</v>
+        <v>0.46</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1446,8 +1431,8 @@
       <c r="K8" s="1">
         <v>0.15</v>
       </c>
-      <c r="L8" s="24" t="s">
-        <v>144</v>
+      <c r="L8" s="21" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1481,10 +1466,10 @@
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="L9" s="24" t="s">
-        <v>145</v>
+        <v>0.25</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1518,10 +1503,10 @@
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="L10" s="24" t="s">
-        <v>146</v>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1556,10 +1541,10 @@
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="1">
-        <v>0.16</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>147</v>
+        <v>0.31</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1593,10 +1578,10 @@
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>148</v>
+        <v>0.04</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1630,10 +1615,10 @@
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>149</v>
+        <v>0.06</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1667,13 +1652,10 @@
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="1">
-        <v>2.69</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="T14" s="1">
-        <v>100</v>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1707,14 +1689,12 @@
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="1">
-        <v>1.33</v>
-      </c>
-      <c r="L15" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="T15" s="19">
-        <v>100</v>
-      </c>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="T15" s="19"/>
     </row>
     <row r="16" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1747,14 +1727,12 @@
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="1">
-        <v>1.42</v>
-      </c>
-      <c r="L16" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="T16" s="19">
-        <v>100</v>
-      </c>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="T16" s="19"/>
     </row>
     <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1787,10 +1765,10 @@
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="L17" s="24" t="s">
-        <v>153</v>
+        <v>0.04</v>
+      </c>
+      <c r="L17" s="21" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1824,17 +1802,12 @@
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="L18" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="T18" s="1">
-        <v>5</v>
-      </c>
-      <c r="U18" s="24" t="s">
-        <v>155</v>
-      </c>
+        <v>0.32</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="U18" s="20"/>
     </row>
     <row r="19" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1868,10 +1841,10 @@
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="L19" s="24" t="s">
-        <v>156</v>
+        <v>0.08</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1906,10 +1879,10 @@
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="1">
-        <v>0.02</v>
-      </c>
-      <c r="L20" s="24" t="s">
-        <v>157</v>
+        <v>0.12</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1944,13 +1917,10 @@
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="L21" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="T21" s="1">
-        <v>10</v>
+        <v>0.34</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1986,8 +1956,8 @@
       <c r="K22" s="1">
         <v>0.08</v>
       </c>
-      <c r="L22" s="24" t="s">
-        <v>159</v>
+      <c r="L22" s="21" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2021,10 +1991,10 @@
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L23" s="24" t="s">
-        <v>160</v>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2058,14 +2028,10 @@
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="1">
-        <f>6.93*0.85</f>
-        <v>5.8904999999999994</v>
-      </c>
-      <c r="L24" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>173</v>
+        <v>7.14</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2099,10 +2065,10 @@
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="1">
-        <v>2.21</v>
-      </c>
-      <c r="L25" s="25" t="s">
-        <v>135</v>
+        <v>3.9</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2136,10 +2102,10 @@
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="L26" s="25" t="s">
-        <v>136</v>
+        <v>0.84</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2173,14 +2139,10 @@
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="1">
-        <f>17.9*0.85</f>
-        <v>15.214999999999998</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>173</v>
+        <v>20.04</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2214,9 +2176,9 @@
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="1">
-        <v>1.94</v>
-      </c>
-      <c r="L28" s="24" t="s">
+        <v>1.82</v>
+      </c>
+      <c r="L28" s="21" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2251,13 +2213,10 @@
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="L29" s="24" t="s">
+        <v>0.41</v>
+      </c>
+      <c r="L29" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="T29" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -2291,62 +2250,62 @@
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L30" s="24" t="s">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="L30" s="21" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20">
+      <c r="A31" s="22">
         <v>35</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="22">
         <v>1</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="22">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="22">
         <v>10</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="H31" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="23">
         <v>16.399999999999999</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="1">
         <v>1.64</v>
       </c>
-      <c r="L31" s="24" t="s">
+      <c r="L31" s="21" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="21"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="23"/>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>36</v>
       </c>
@@ -2377,13 +2336,13 @@
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="L33" s="24" t="s">
+        <v>0.1</v>
+      </c>
+      <c r="L33" s="21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>37</v>
       </c>
@@ -2414,13 +2373,13 @@
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="L34" s="24" t="s">
+        <v>0.32</v>
+      </c>
+      <c r="L34" s="21" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>38</v>
       </c>
@@ -2451,13 +2410,13 @@
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="1">
-        <v>0.19</v>
-      </c>
-      <c r="L35" s="24" t="s">
+        <v>0.16</v>
+      </c>
+      <c r="L35" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>41</v>
       </c>
@@ -2488,16 +2447,13 @@
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="L36" s="24" t="s">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L36" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="T36" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>42</v>
       </c>
@@ -2528,16 +2484,13 @@
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="L37" s="24" t="s">
+        <v>0.23</v>
+      </c>
+      <c r="L37" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="T37" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46</v>
       </c>
@@ -2568,16 +2521,13 @@
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="1">
-        <v>2.95</v>
-      </c>
-      <c r="L38" s="24" t="s">
+        <v>0.6</v>
+      </c>
+      <c r="L38" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="T38" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>48</v>
       </c>
@@ -2606,19 +2556,19 @@
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="1">
-        <v>0.77</v>
-      </c>
-      <c r="L39" s="24" t="s">
+        <v>0.39</v>
+      </c>
+      <c r="L39" s="21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="J40" s="5"/>
     </row>
-    <row r="41" spans="1:20" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J41" s="5"/>
     </row>
-    <row r="42" spans="1:20" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I42" s="9">
         <f>SUM(I2:I39)</f>
         <v>160.04000000000002</v>
@@ -2626,10 +2576,10 @@
       <c r="J42" s="5"/>
       <c r="K42" s="9">
         <f>SUM(K2:K39)</f>
-        <v>48.945499999999988</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>48.159999999999989</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="7"/>
       <c r="C43" s="6"/>
@@ -2641,7 +2591,7 @@
       <c r="I43" s="6"/>
       <c r="J43" s="8"/>
     </row>
-    <row r="44" spans="1:20" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:12" ht="21" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="G31:G32"/>
@@ -2658,8 +2608,43 @@
     <hyperlink ref="H28" r:id="rId1" display="https://www.mouser.de/ProductDetail/STMicroelectronics/TSC2012IDT?qs=%252B6g0mu59x7KSqOHhuXDI4w%3D%3D" xr:uid="{09362BA6-A9EB-4F51-AF68-921D4861D3C9}"/>
     <hyperlink ref="L25" r:id="rId2" xr:uid="{1304E72E-0C1D-4C2F-BBA2-99E6DD255403}"/>
     <hyperlink ref="L26" r:id="rId3" xr:uid="{56EBBF5D-81A9-4D52-8480-A82B49AEB529}"/>
+    <hyperlink ref="L2" r:id="rId4" xr:uid="{A4A9B1DC-9EA4-4802-A284-F0F8AEBA4877}"/>
+    <hyperlink ref="L3" r:id="rId5" xr:uid="{DE814A4B-6567-4CCE-8DE3-378CD0F2C182}"/>
+    <hyperlink ref="L4" r:id="rId6" xr:uid="{1A7D470B-A38D-4295-A026-A009E7E3350E}"/>
+    <hyperlink ref="L5" r:id="rId7" xr:uid="{C2F548AE-1571-4B5D-8F5C-6C827EFB07D8}"/>
+    <hyperlink ref="L6" r:id="rId8" xr:uid="{54323170-AFF3-4F65-B10E-63F4376CFCC8}"/>
+    <hyperlink ref="L7" r:id="rId9" xr:uid="{1F1139B5-E066-4524-9A1D-701484A87063}"/>
+    <hyperlink ref="L8" r:id="rId10" xr:uid="{28D3692B-865F-4BF2-BEDF-648ED25C6216}"/>
+    <hyperlink ref="L9" r:id="rId11" xr:uid="{E0D6A0B3-B9ED-403A-AEFB-839A6B0E2732}"/>
+    <hyperlink ref="L10" r:id="rId12" xr:uid="{3237A9AE-9608-414D-BFFE-725DAF963746}"/>
+    <hyperlink ref="L11" r:id="rId13" xr:uid="{8047DAB6-66B3-4FAB-95B1-43D42F446405}"/>
+    <hyperlink ref="L12" r:id="rId14" xr:uid="{5785426D-163D-483E-9E90-97C2DEACADEF}"/>
+    <hyperlink ref="L13" r:id="rId15" xr:uid="{932C61B8-948D-4C0A-97AA-EED98E54296B}"/>
+    <hyperlink ref="L14" r:id="rId16" xr:uid="{71A19693-BB2B-4350-BA0B-A4025851366B}"/>
+    <hyperlink ref="L15" r:id="rId17" xr:uid="{1630104D-E111-4DDE-B78F-B6B98AD049C9}"/>
+    <hyperlink ref="L16" r:id="rId18" xr:uid="{297AB614-8A9A-4FBC-B86B-44A12AC59429}"/>
+    <hyperlink ref="L17" r:id="rId19" xr:uid="{91FE7A44-65EF-4E04-B957-70FBBAB9056B}"/>
+    <hyperlink ref="L18" r:id="rId20" xr:uid="{9E9382E5-FA05-4FE9-BF6D-268341FE7FED}"/>
+    <hyperlink ref="L19" r:id="rId21" xr:uid="{E404645C-E7E8-4466-8177-5E3B1EC1AA4E}"/>
+    <hyperlink ref="L20" r:id="rId22" xr:uid="{81AF7CC2-C3A3-455F-B8F9-ADA4EA8A3CF1}"/>
+    <hyperlink ref="L21" r:id="rId23" xr:uid="{C18D619A-A10A-49DE-B8D6-668226EE79BD}"/>
+    <hyperlink ref="L22" r:id="rId24" xr:uid="{F9E71924-5DA1-4874-AAD9-A7C85D928A8F}"/>
+    <hyperlink ref="L23" r:id="rId25" xr:uid="{4B7D7763-CC42-4D40-B1F0-48849B57C8D0}"/>
+    <hyperlink ref="L24" r:id="rId26" xr:uid="{28B8AFB7-EBB3-4143-ABA6-27614B4DC33E}"/>
+    <hyperlink ref="L27" r:id="rId27" xr:uid="{4EDC7A8B-DF38-4B84-A2F0-02E723F26576}"/>
+    <hyperlink ref="L28" r:id="rId28" xr:uid="{CBC3B3B6-0B1D-4132-B3E4-A95E0442D55F}"/>
+    <hyperlink ref="L29" r:id="rId29" xr:uid="{698EE5D7-7F82-4D06-BF7F-3C5CB0499C4B}"/>
+    <hyperlink ref="L30" r:id="rId30" xr:uid="{E76E4496-10B2-42D9-A67A-2A10CA0D5044}"/>
+    <hyperlink ref="L31" r:id="rId31" xr:uid="{E12FA257-62E6-4D1A-B872-0955F94A5442}"/>
+    <hyperlink ref="L33" r:id="rId32" xr:uid="{C5B1811F-608D-4A91-B9B9-16E91A89A86E}"/>
+    <hyperlink ref="L34" r:id="rId33" xr:uid="{AC5E4135-5171-4BCA-8BDC-1618C9E63E56}"/>
+    <hyperlink ref="L35" r:id="rId34" xr:uid="{AC796BAD-32C7-4D2B-9B65-A817489A6A27}"/>
+    <hyperlink ref="L36" r:id="rId35" xr:uid="{F6D4681D-3608-447A-9892-1B32092C45BE}"/>
+    <hyperlink ref="L37" r:id="rId36" xr:uid="{A5344DAF-D1DC-480D-B2CA-D7FEA821592B}"/>
+    <hyperlink ref="L38" r:id="rId37" xr:uid="{3703AE3F-3B74-47B8-8693-99E3397D2FC3}"/>
+    <hyperlink ref="L39" r:id="rId38" xr:uid="{3EE8E5EA-9297-4995-9535-3DBF461FC62C}"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId4"/>
+  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId39"/>
 </worksheet>
 </file>